--- a/grupos/5APM - Estadisticos 20221.xlsx
+++ b/grupos/5APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -113,7 +113,7 @@
     <t>VERA PONCE MARITZA</t>
   </si>
   <si>
-    <t>XILCAHUA TLAXCALA LUIS ANGEL</t>
+    <t>XICALHUA TLAXCALA LUIS ANGEL</t>
   </si>
   <si>
     <t>XOTLANIHUA MARTINEZ ANGELA MONTSERRAT</t>
@@ -149,12 +149,12 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
@@ -290,7 +290,7 @@
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>XILCAHUA</t>
+    <t>XICALHUA</t>
   </si>
   <si>
     <t>ZAVALETA</t>
@@ -851,10 +851,10 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -890,7 +890,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -928,10 +928,10 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -967,7 +967,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -999,16 +999,16 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1044,7 +1044,7 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1076,16 +1076,16 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1112,7 +1112,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>7</v>
@@ -1121,7 +1121,7 @@
         <v>7</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1159,10 +1159,10 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1198,7 +1198,7 @@
         <v>6</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>6</v>
@@ -1230,16 +1230,16 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1275,7 +1275,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1313,10 +1313,10 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1352,7 +1352,7 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1390,10 +1390,10 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1429,7 +1429,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1467,10 +1467,10 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1503,10 +1503,10 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1538,16 +1538,16 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1574,7 +1574,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>9</v>
@@ -1583,7 +1583,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1621,10 +1621,10 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1692,16 +1692,16 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1728,7 +1728,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1737,7 +1737,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1769,16 +1769,16 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1852,7 +1852,7 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1888,7 +1888,7 @@
         <v>6</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>-1</v>
@@ -1923,16 +1923,16 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -1959,7 +1959,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -2000,16 +2000,16 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2036,7 +2036,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>8</v>
@@ -2077,16 +2077,16 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2113,7 +2113,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>9</v>
@@ -2122,7 +2122,7 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2160,10 +2160,10 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2199,7 +2199,7 @@
         <v>7</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2237,7 +2237,7 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2308,16 +2308,16 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2344,7 +2344,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2353,7 +2353,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2385,13 +2385,13 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -2524,7 +2524,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
@@ -2533,30 +2533,30 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="G3">
-        <v>9.52</v>
+        <v>19.05</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
@@ -2565,25 +2565,25 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>80.95</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G4">
-        <v>19.05</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2661,16 +2661,16 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="H7">
         <v>6.7</v>
@@ -2893,7 +2893,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2953,7 +2953,7 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2973,7 +2973,7 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -3371,7 +3371,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3403,16 +3403,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920337</v>
+        <v>20330051920336</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920337</v>
+        <v>20330051920336</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3449,16 +3449,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330050470596</v>
+        <v>20330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -3472,19 +3472,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330050470596</v>
+        <v>20330051920337</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>43</v>
@@ -3602,7 +3602,7 @@
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -3610,24 +3610,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920383</v>
+        <v>19330050470596</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
         <v>70</v>
       </c>
       <c r="D11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920383</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
         <v>82</v>
       </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11">
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20221.xlsx
+++ b/grupos/5APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -152,13 +152,13 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
     <t>Ortega Valle Manuel</t>
@@ -848,7 +848,7 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -860,7 +860,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -884,7 +884,7 @@
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -896,7 +896,7 @@
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -925,7 +925,7 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -937,7 +937,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1002,7 +1002,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -1014,7 +1014,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1038,7 +1038,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1079,7 +1079,7 @@
         <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -1091,7 +1091,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1115,7 +1115,7 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>7</v>
@@ -1156,7 +1156,7 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1168,7 +1168,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1192,7 +1192,7 @@
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -1233,7 +1233,7 @@
         <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
         <v>7</v>
@@ -1245,7 +1245,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1269,7 +1269,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1281,7 +1281,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1310,7 +1310,7 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1322,7 +1322,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1358,7 +1358,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1387,7 +1387,7 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1399,7 +1399,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1464,7 +1464,7 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>7</v>
@@ -1476,7 +1476,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1500,7 +1500,7 @@
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1512,7 +1512,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1541,7 +1541,7 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
         <v>7</v>
@@ -1553,7 +1553,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1577,7 +1577,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1618,7 +1618,7 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>7</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1666,7 +1666,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1695,7 +1695,7 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -1707,7 +1707,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1772,7 +1772,7 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -1784,7 +1784,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1808,7 +1808,7 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1849,7 +1849,7 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -1861,7 +1861,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1885,7 +1885,7 @@
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -1926,7 +1926,7 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -1938,7 +1938,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1962,7 +1962,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -2003,7 +2003,7 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
         <v>7</v>
@@ -2015,7 +2015,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2039,7 +2039,7 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2080,7 +2080,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2092,7 +2092,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2116,7 +2116,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2157,7 +2157,7 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>6</v>
@@ -2169,7 +2169,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2193,7 +2193,7 @@
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2205,7 +2205,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2234,7 +2234,7 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
         <v>7</v>
@@ -2246,7 +2246,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2270,7 +2270,7 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -2311,7 +2311,7 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>7</v>
@@ -2323,7 +2323,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2347,7 +2347,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2388,7 +2388,7 @@
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>7</v>
@@ -2400,7 +2400,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2424,7 +2424,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2436,7 +2436,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
@@ -2568,27 +2568,27 @@
         <v>18</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>85.70999999999999</v>
       </c>
       <c r="G4">
+        <v>14.29</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>8.1</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
       <c r="J4">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -2597,30 +2597,30 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>90.48</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G5">
-        <v>9.52</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2629,19 +2629,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>90.48</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="G6">
-        <v>9.52</v>
+        <v>4.76</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2893,7 +2893,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2953,7 +2953,7 @@
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2973,7 +2973,7 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3371,7 +3371,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3495,16 +3495,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920340</v>
+        <v>20330051920345</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -3518,39 +3518,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920381</v>
+        <v>20330051920345</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920347</v>
+        <v>20330051920356</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -3564,22 +3564,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920349</v>
+        <v>20330051920356</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920354</v>
+        <v>20330051920383</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -3610,22 +3610,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330050470596</v>
+        <v>20330051920383</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
         <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -3633,24 +3633,139 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920383</v>
+        <v>20330051920340</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920381</v>
+      </c>
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920347</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920349</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920354</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330050470596</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
         <v>70</v>
       </c>
-      <c r="D12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12">
+      <c r="D17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20221.xlsx
+++ b/grupos/5APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -857,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>7</v>
@@ -893,7 +893,7 @@
         <v>7</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -934,7 +934,7 @@
         <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -1011,7 +1011,7 @@
         <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>9</v>
@@ -1088,7 +1088,7 @@
         <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>7</v>
@@ -1124,7 +1124,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1165,7 +1165,7 @@
         <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -1242,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>8</v>
@@ -1319,7 +1319,7 @@
         <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1396,7 +1396,7 @@
         <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -1432,7 +1432,7 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1473,7 +1473,7 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -1509,7 +1509,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1550,7 +1550,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1627,7 +1627,7 @@
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1663,7 +1663,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1704,7 +1704,7 @@
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -1781,7 +1781,7 @@
         <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -1858,7 +1858,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -1935,7 +1935,7 @@
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>6</v>
@@ -2012,7 +2012,7 @@
         <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>9</v>
@@ -2089,7 +2089,7 @@
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2166,7 +2166,7 @@
         <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>7</v>
@@ -2243,7 +2243,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>7</v>
@@ -2279,7 +2279,7 @@
         <v>-1</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2320,7 +2320,7 @@
         <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -2397,7 +2397,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>8</v>
@@ -2433,7 +2433,7 @@
         <v>-1</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2533,19 +2533,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>80.95</v>
+        <v>61.9</v>
       </c>
       <c r="G3">
-        <v>19.05</v>
+        <v>38.1</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3371,7 +3371,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3403,16 +3403,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920336</v>
+        <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -3426,16 +3426,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920336</v>
+        <v>20330051920337</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3449,16 +3449,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920337</v>
+        <v>20330051920345</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -3472,22 +3472,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920337</v>
+        <v>20330051920345</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3495,16 +3495,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920345</v>
+        <v>20330051920381</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -3518,22 +3518,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920345</v>
+        <v>20330051920381</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3541,16 +3541,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920356</v>
+        <v>20330051920347</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -3564,114 +3564,114 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920356</v>
+        <v>20330051920347</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920383</v>
+        <v>20330051920349</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920383</v>
+        <v>20330051920349</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920340</v>
+        <v>20330051920383</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920381</v>
+        <v>20330051920383</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -3679,16 +3679,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920347</v>
+        <v>20330051920336</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -3702,16 +3702,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920349</v>
+        <v>20330051920340</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
@@ -3725,16 +3725,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920354</v>
+        <v>20330051920341</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -3748,24 +3748,47 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
+        <v>20330051920354</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
         <v>19330050470596</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>59</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>70</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>80</v>
       </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="E18" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s">
         <v>42</v>
       </c>
-      <c r="G17">
+      <c r="G18">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20221.xlsx
+++ b/grupos/5APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -146,24 +146,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
+    <t>Ortega Valle Manuel</t>
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -182,27 +182,54 @@
     <t>BARRAGAN</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>CUEVAS</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
     <t>NAMIGTLE</t>
   </si>
   <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>URBANO</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -212,39 +239,69 @@
     <t>VILLALBA</t>
   </si>
   <si>
+    <t>ZAVALETA</t>
+  </si>
+  <si>
     <t>CUATRA</t>
   </si>
   <si>
+    <t>PIMENTEL</t>
+  </si>
+  <si>
+    <t>AGUIRRE</t>
+  </si>
+  <si>
     <t>IXTLA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>ESTRELLA</t>
+  </si>
+  <si>
     <t>MOLOHUA</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>PONCE</t>
   </si>
   <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
     <t>YAIR</t>
   </si>
   <si>
     <t>ADAN</t>
   </si>
   <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
     <t>CESAR</t>
   </si>
   <si>
+    <t>ISYSS MONSERRATH</t>
+  </si>
+  <si>
+    <t>MARIAM GUADALUPE</t>
+  </si>
+  <si>
     <t>ELIEL</t>
   </si>
   <si>
@@ -254,94 +311,37 @@
     <t>EVELYN</t>
   </si>
   <si>
+    <t>JESUS</t>
+  </si>
+  <si>
     <t>ANGEL ALDAHIR</t>
   </si>
   <si>
+    <t>ESTEFANI</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
+  </si>
+  <si>
     <t>INGRID</t>
   </si>
   <si>
+    <t>JAHEL</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
     <t>OMAR ALDAIR</t>
   </si>
   <si>
     <t>MARITZA</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>ANGELA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>URBANO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>XICALHUA</t>
-  </si>
-  <si>
-    <t>ZAVALETA</t>
-  </si>
-  <si>
-    <t>PIMENTEL</t>
-  </si>
-  <si>
-    <t>AGUIRRE</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
-  </si>
-  <si>
-    <t>ISYSS MONSERRATH</t>
-  </si>
-  <si>
-    <t>MARIAM GUADALUPE</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>ESTEFANI</t>
-  </si>
-  <si>
-    <t>EMILIO</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
 </sst>
 </file>
@@ -827,7 +827,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -845,7 +845,7 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -881,7 +881,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -904,7 +904,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>7</v>
@@ -922,7 +922,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -958,7 +958,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1135,7 +1135,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -1153,7 +1153,7 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>6</v>
@@ -1189,7 +1189,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1289,7 +1289,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -1307,7 +1307,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -1343,7 +1343,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1366,7 +1366,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1384,7 +1384,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
         <v>7</v>
@@ -1420,7 +1420,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1443,7 +1443,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1461,7 +1461,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -1497,7 +1497,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1597,7 +1597,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -1615,7 +1615,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>8</v>
@@ -1651,7 +1651,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1828,7 +1828,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -1837,7 +1837,7 @@
         <v>6</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>4</v>
@@ -1855,7 +1855,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -1882,7 +1882,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -1891,7 +1891,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -2136,7 +2136,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -2154,7 +2154,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>9</v>
@@ -2190,7 +2190,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2213,7 +2213,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -2222,7 +2222,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>6</v>
@@ -2231,7 +2231,7 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>9</v>
@@ -2240,7 +2240,7 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -2267,7 +2267,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2276,7 +2276,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2376,7 +2376,7 @@
         <v>7</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>6</v>
@@ -2394,7 +2394,7 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>8</v>
@@ -2430,7 +2430,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2492,7 +2492,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>42</v>
@@ -2501,30 +2501,30 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>52.38</v>
+        <v>61.9</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>38.1</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>47.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
@@ -2533,19 +2533,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>61.9</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G3">
-        <v>38.1</v>
+        <v>14.29</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
@@ -2565,19 +2565,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="G4">
-        <v>14.29</v>
+        <v>4.76</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -2597,30 +2597,30 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2641,7 +2641,7 @@
         <v>4.76</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>47</v>
@@ -2673,7 +2673,7 @@
         <v>4.76</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2689,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2714,266 +2714,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920336</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920337</v>
-      </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920340</v>
-      </c>
-      <c r="B4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920345</v>
-      </c>
-      <c r="B5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920381</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920347</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920349</v>
-      </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920353</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920353</v>
-      </c>
-      <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330050470596</v>
-      </c>
-      <c r="B11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920356</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920356</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920383</v>
-      </c>
-      <c r="B14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3009,200 +2749,200 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920353</v>
+        <v>20330051920336</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920356</v>
+        <v>20330051920337</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920336</v>
+        <v>20330051920263</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920337</v>
+        <v>20330051920340</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920340</v>
+        <v>20330051920341</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920345</v>
+        <v>20330051920344</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920381</v>
+        <v>20330051920345</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920347</v>
+        <v>20330051920381</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920349</v>
+        <v>20330051920347</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330050470596</v>
+        <v>20330051920348</v>
       </c>
       <c r="B11" t="s">
         <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920383</v>
+        <v>20330051920349</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920263</v>
+        <v>20330051920350</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
         <v>99</v>
@@ -3213,13 +2953,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920341</v>
+        <v>20330051920352</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>100</v>
@@ -3230,13 +2970,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920344</v>
+        <v>20330051920353</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
         <v>101</v>
@@ -3247,13 +2987,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920348</v>
+        <v>20330051920354</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>102</v>
@@ -3264,16 +3004,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920350</v>
+        <v>20330051920355</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -3281,16 +3021,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920352</v>
+        <v>20330051920382</v>
       </c>
       <c r="B18" t="s">
         <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -3298,16 +3038,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920354</v>
+        <v>19330050470596</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -3315,16 +3055,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920355</v>
+        <v>20330051920356</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -3332,13 +3072,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920382</v>
+        <v>20330051920357</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
         <v>106</v>
@@ -3349,13 +3089,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920357</v>
+        <v>20330051920383</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
         <v>107</v>
@@ -3371,7 +3111,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3403,42 +3143,42 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920337</v>
+        <v>20330051920345</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920337</v>
+        <v>20330051920345</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>43</v>
@@ -3449,45 +3189,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920345</v>
+        <v>20330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>42</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920345</v>
+        <v>20330051920341</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3498,42 +3238,42 @@
         <v>20330051920381</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>42</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920381</v>
+        <v>20330051920347</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3541,45 +3281,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920347</v>
+        <v>20330051920349</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>42</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920347</v>
+        <v>20330051920354</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -3587,209 +3327,48 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920349</v>
+        <v>20330051920356</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>42</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920349</v>
+        <v>20330051920383</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>43</v>
       </c>
       <c r="G11">
         <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920383</v>
-      </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920383</v>
-      </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920336</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920340</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920341</v>
-      </c>
-      <c r="B16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920354</v>
-      </c>
-      <c r="B17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330050470596</v>
-      </c>
-      <c r="B18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5APM - Estadisticos 20221.xlsx
+++ b/grupos/5APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -149,16 +149,16 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>
@@ -866,13 +866,13 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -890,7 +890,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -943,7 +943,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1020,7 +1020,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1038,7 +1038,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1097,7 +1097,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1174,13 +1174,13 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1251,7 +1251,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1328,13 +1328,13 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1346,13 +1346,13 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1405,13 +1405,13 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1429,7 +1429,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1482,7 +1482,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1559,13 +1559,13 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1636,13 +1636,13 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1660,7 +1660,7 @@
         <v>7</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>5</v>
@@ -1713,7 +1713,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1790,7 +1790,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1808,7 +1808,7 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1867,7 +1867,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1944,13 +1944,13 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -1962,13 +1962,13 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>6</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -2021,7 +2021,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2098,13 +2098,13 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2175,13 +2175,13 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2193,13 +2193,13 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2252,7 +2252,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2329,13 +2329,13 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2406,7 +2406,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2424,7 +2424,7 @@
         <v>6</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2524,7 +2524,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
@@ -2533,19 +2533,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>85.70999999999999</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="G3">
-        <v>14.29</v>
+        <v>4.76</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
@@ -2577,7 +2577,7 @@
         <v>4.76</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -2609,7 +2609,7 @@
         <v>4.76</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2641,7 +2641,7 @@
         <v>4.76</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>4.76</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3111,7 +3111,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920345</v>
+        <v>20330051920337</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3166,22 +3166,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920345</v>
+        <v>20330051920341</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920337</v>
+        <v>20330051920345</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3212,16 +3212,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920341</v>
+        <v>20330051920381</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -3235,16 +3235,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920381</v>
+        <v>20330051920347</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -3258,16 +3258,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920347</v>
+        <v>20330051920349</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -3281,16 +3281,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920349</v>
+        <v>20330051920354</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -3304,16 +3304,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920354</v>
+        <v>20330051920356</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -3322,52 +3322,6 @@
         <v>42</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920356</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920383</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>107</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APM - Estadisticos 20221.xlsx
+++ b/grupos/5APM - Estadisticos 20221.xlsx
@@ -949,7 +949,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1026,7 +1026,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1103,7 +1103,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1257,7 +1257,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1488,7 +1488,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1719,7 +1719,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1796,7 +1796,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1873,7 +1873,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2027,7 +2027,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2258,7 +2258,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2276,7 +2276,7 @@
         <v>7</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2412,7 +2412,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2430,7 +2430,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>7</v>
@@ -2673,7 +2673,7 @@
         <v>4.76</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5APM - Estadisticos 20221.xlsx
+++ b/grupos/5APM - Estadisticos 20221.xlsx
@@ -149,19 +149,19 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
     <t>NC</t>
@@ -863,13 +863,13 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>10</v>
@@ -881,7 +881,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -940,13 +940,13 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -1017,13 +1017,13 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>9</v>
@@ -1035,7 +1035,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -1094,13 +1094,13 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>9</v>
@@ -1171,13 +1171,13 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>7</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1189,7 +1189,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1248,13 +1248,13 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>9</v>
@@ -1266,13 +1266,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>9</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1325,13 +1325,13 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1343,7 +1343,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>6</v>
@@ -1402,13 +1402,13 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
         <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1479,13 +1479,13 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -1497,7 +1497,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1556,13 +1556,13 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1633,13 +1633,13 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>10</v>
@@ -1710,13 +1710,13 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>9</v>
@@ -1728,7 +1728,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1787,13 +1787,13 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>9</v>
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>5</v>
@@ -1941,13 +1941,13 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -1959,13 +1959,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2018,13 +2018,13 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
         <v>9</v>
@@ -2095,13 +2095,13 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2113,7 +2113,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2172,13 +2172,13 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>10</v>
@@ -2190,7 +2190,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2249,13 +2249,13 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>9</v>
@@ -2267,7 +2267,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2326,13 +2326,13 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2344,7 +2344,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>10</v>
@@ -2403,13 +2403,13 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2421,7 +2421,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -2524,7 +2524,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
@@ -2533,19 +2533,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>95.23999999999999</v>
+        <v>90.48</v>
       </c>
       <c r="G3">
-        <v>4.76</v>
+        <v>9.52</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
@@ -2577,7 +2577,7 @@
         <v>4.76</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -2609,7 +2609,7 @@
         <v>4.76</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2641,7 +2641,7 @@
         <v>4.76</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>47</v>
@@ -2661,19 +2661,19 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920337</v>
+        <v>20330051920354</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3166,16 +3166,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920341</v>
+        <v>20330051920354</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920345</v>
+        <v>20330051920337</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3212,16 +3212,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920381</v>
+        <v>20330051920341</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -3235,16 +3235,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920347</v>
+        <v>20330051920381</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -3258,16 +3258,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920349</v>
+        <v>20330051920347</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -3281,16 +3281,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920354</v>
+        <v>20330051920349</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>

--- a/grupos/5APM - Estadisticos 20221.xlsx
+++ b/grupos/5APM - Estadisticos 20221.xlsx
@@ -878,7 +878,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -896,7 +896,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -955,7 +955,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>7</v>
@@ -1032,7 +1032,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1050,7 +1050,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1109,7 +1109,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1186,7 +1186,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1204,7 +1204,7 @@
         <v>6</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1263,7 +1263,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1340,7 +1340,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1417,7 +1417,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1494,7 +1494,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1571,7 +1571,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1666,7 +1666,7 @@
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1725,7 +1725,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1802,7 +1802,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1879,7 +1879,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1956,7 +1956,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -1974,7 +1974,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2033,7 +2033,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2110,7 +2110,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2187,7 +2187,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -2264,7 +2264,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>8</v>
@@ -2341,7 +2341,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2418,7 +2418,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>7</v>
@@ -2436,7 +2436,7 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2577,7 +2577,7 @@
         <v>4.76</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>

--- a/grupos/5APM - Estadisticos 20221.xlsx
+++ b/grupos/5APM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -146,22 +146,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>NC</t>
@@ -875,7 +875,7 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>6</v>
@@ -952,7 +952,7 @@
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>7</v>
@@ -970,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1029,7 +1029,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -1047,7 +1047,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1106,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>7</v>
@@ -1124,7 +1124,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1183,7 +1183,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>9</v>
@@ -1260,7 +1260,7 @@
         <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>10</v>
@@ -1337,7 +1337,7 @@
         <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
         <v>8</v>
@@ -1414,7 +1414,7 @@
         <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>9</v>
@@ -1432,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1491,7 +1491,7 @@
         <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>8</v>
@@ -1509,7 +1509,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1568,7 +1568,7 @@
         <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>10</v>
@@ -1586,7 +1586,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1645,7 +1645,7 @@
         <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>9</v>
@@ -1663,7 +1663,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1722,7 +1722,7 @@
         <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
         <v>9</v>
@@ -1799,7 +1799,7 @@
         <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>10</v>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1846,7 +1846,7 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>5</v>
@@ -1864,7 +1864,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -1876,13 +1876,13 @@
         <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>5</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -1953,7 +1953,7 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>8</v>
@@ -1971,7 +1971,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2030,7 +2030,7 @@
         <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>10</v>
@@ -2107,7 +2107,7 @@
         <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>10</v>
@@ -2184,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>7</v>
@@ -2202,7 +2202,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2261,7 +2261,7 @@
         <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>9</v>
@@ -2279,7 +2279,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2338,7 +2338,7 @@
         <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>10</v>
@@ -2356,7 +2356,7 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2415,7 +2415,7 @@
         <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>9</v>
@@ -2492,7 +2492,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>42</v>
@@ -2501,16 +2501,16 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>61.9</v>
+        <v>90.48</v>
       </c>
       <c r="G2">
-        <v>38.1</v>
+        <v>9.52</v>
       </c>
       <c r="H2">
         <v>6.7</v>
@@ -2524,7 +2524,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
@@ -2533,19 +2533,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>90.48</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="G3">
-        <v>9.52</v>
+        <v>4.76</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
@@ -2577,7 +2577,7 @@
         <v>4.76</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2588,7 +2588,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>45</v>
@@ -2609,7 +2609,7 @@
         <v>4.76</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -2641,7 +2641,7 @@
         <v>4.76</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2652,7 +2652,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>47</v>
@@ -2661,19 +2661,19 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3111,7 +3111,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3158,170 +3158,9 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920354</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920337</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920341</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920381</v>
-      </c>
-      <c r="B6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920347</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920349</v>
-      </c>
-      <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920356</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>
